--- a/metadata/metadata_Macaca_mulatta.xlsx
+++ b/metadata/metadata_Macaca_mulatta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ms84/Research/postdoc/projects/PrimateSomatic/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C649A3CE-4E1B-7148-A346-BC042BC1EAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BD4D0C-CBB8-AE42-AF16-F3E8679E17D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31800" yWindow="1840" windowWidth="28040" windowHeight="15040" xr2:uid="{DE405C7A-DE7E-F046-BCC9-57957EBF65EE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" xr2:uid="{DE405C7A-DE7E-F046-BCC9-57957EBF65EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="54">
   <si>
     <t>MQD0001d</t>
   </si>
@@ -195,13 +195,16 @@
   </si>
   <si>
     <t>tissue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -215,13 +218,32 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFF2F2F2"/>
+      <name val="Monaco"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -236,9 +258,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,36 +597,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A9E92B-56C3-8F45-A079-EB342AC7C619}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -621,8 +650,13 @@
       <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
@@ -641,8 +675,10 @@
       <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -661,8 +697,10 @@
       <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" s="1"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -681,8 +719,10 @@
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5" s="1"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
@@ -701,8 +741,10 @@
       <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" s="1"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -721,8 +763,10 @@
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7" s="1"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
@@ -741,8 +785,10 @@
       <c r="F8" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" s="1"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -761,8 +807,10 @@
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9" s="1"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -781,8 +829,10 @@
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" s="1"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -801,8 +851,10 @@
       <c r="F11" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G11" s="1"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -821,8 +873,10 @@
       <c r="F12" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>41</v>
       </c>
@@ -841,8 +895,10 @@
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="1"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>41</v>
       </c>
@@ -861,8 +917,10 @@
       <c r="F14" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="1"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -881,8 +939,10 @@
       <c r="F15" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="1"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
@@ -901,8 +961,10 @@
       <c r="F16" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -921,8 +983,10 @@
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -941,8 +1005,10 @@
       <c r="F18" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>41</v>
       </c>
@@ -961,6 +1027,8 @@
       <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
